--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835BAF0D-AB13-4D27-8069-6772164C369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>kind</t>
   </si>
@@ -92,8 +86,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,14 +419,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,7 +449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -478,7 +472,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -501,7 +495,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -524,7 +518,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -544,7 +538,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -564,15 +558,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7">
         <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
       </c>
       <c r="D7">
         <v>30</v>
@@ -587,11 +578,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -599,7 +590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -607,7 +598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -615,7 +606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -623,7 +614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -631,7 +622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -639,7 +630,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>5</v>
       </c>

--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,101 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835BAF0D-AB13-4D27-8069-6772164C369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>variant_qualifier</t>
-  </si>
-  <si>
-    <t>size_variant_1</t>
-  </si>
-  <si>
-    <t>size_variant_2</t>
-  </si>
-  <si>
-    <t>size_variant_3</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>purpose</t>
-  </si>
-  <si>
-    <t>Row selector field</t>
-  </si>
-  <si>
-    <t>Fills the Select Unit combobox</t>
-  </si>
-  <si>
-    <t>First size variant to create</t>
-  </si>
-  <si>
-    <t>Second size variant to create</t>
-  </si>
-  <si>
-    <t>Third size variant to create</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>Black-baggy</t>
-  </si>
-  <si>
-    <t>Black-Plain</t>
-  </si>
-  <si>
-    <t>White-Plain</t>
-  </si>
-  <si>
-    <t>Beige</t>
-  </si>
-  <si>
-    <t>size_variant_4</t>
-  </si>
-  <si>
-    <t>Trouser</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,21 +66,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -216,6 +151,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,6 +186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -284,20 +221,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -419,235 +352,346 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G8"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="B1" t="str">
+        <v>size</v>
+      </c>
+      <c r="C1" t="str">
+        <v>variant_qualifier</v>
+      </c>
+      <c r="D1" t="str">
+        <v>size_variant_1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>size_variant_2</v>
+      </c>
+      <c r="F1" t="str">
+        <v>size_variant_3</v>
+      </c>
+      <c r="G1" t="str">
+        <v>size_variant_4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Beige</v>
+      </c>
+      <c r="B2" t="str">
+        <v>28</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D2" t="str">
         <v>26</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="str">
         <v>30</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <v>32</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="B3" t="str">
+        <v>28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D3" t="str">
         <v>26</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="str">
         <v>30</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
         <v>32</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Black-baggy</v>
+      </c>
+      <c r="B4" t="str">
+        <v>28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D4" t="str">
         <v>26</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="str">
         <v>30</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
         <v>32</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Black-Plain</v>
+      </c>
+      <c r="B5" t="str">
+        <v>28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D5" t="str">
         <v>26</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="str">
         <v>30</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
+    <row r="6">
+      <c r="A6" t="str">
+        <v>White-Plain</v>
+      </c>
+      <c r="B6" t="str">
+        <v>28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D6" t="str">
         <v>26</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="str">
         <v>30</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="str">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Trouser</v>
+      </c>
+      <c r="B7" t="str">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
+      <c r="C7" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D7" t="str">
         <v>30</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="str">
         <v>32</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Trouser</v>
+      </c>
+      <c r="B8" t="str">
+        <v>M</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="D8" t="str">
+        <v>L</v>
+      </c>
+      <c r="E8" t="str">
+        <v>XL</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>purpose</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>kind</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Row selector field</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>size</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Row selector field</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>variant_qualifier</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Fills the Select Unit combobox</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>size_variant_1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>First size variant to create</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>size_variant_2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Second size variant to create</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>size_variant_3</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Third size variant to create</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,41 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="525" windowWidth="19815" windowHeight="7365"/>
+  </bookViews>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>variant_qualifier</t>
+  </si>
+  <si>
+    <t>size_variant_1</t>
+  </si>
+  <si>
+    <t>size_variant_2</t>
+  </si>
+  <si>
+    <t>size_variant_3</t>
+  </si>
+  <si>
+    <t>size_variant_4</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>Black-baggy</t>
+  </si>
+  <si>
+    <t>Black-Plain</t>
+  </si>
+  <si>
+    <t>White-Plain</t>
+  </si>
+  <si>
+    <t>Trouser</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>purpose</t>
+  </si>
+  <si>
+    <t>Row selector field</t>
+  </si>
+  <si>
+    <t>Fills the Select Unit combobox</t>
+  </si>
+  <si>
+    <t>First size variant to create</t>
+  </si>
+  <si>
+    <t>Second size variant to create</t>
+  </si>
+  <si>
+    <t>Third size variant to create</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -399,204 +474,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.375" customWidth="1"/>
+    <col min="2" max="26" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>kind</v>
-      </c>
-      <c r="B1" t="str">
-        <v>size</v>
-      </c>
-      <c r="C1" t="str">
-        <v>variant_qualifier</v>
-      </c>
-      <c r="D1" t="str">
-        <v>size_variant_1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>size_variant_2</v>
-      </c>
-      <c r="F1" t="str">
-        <v>size_variant_3</v>
-      </c>
-      <c r="G1" t="str">
-        <v>size_variant_4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Beige</v>
-      </c>
-      <c r="B2" t="str">
-        <v>28</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D2" t="str">
-        <v>26</v>
-      </c>
-      <c r="E2" t="str">
-        <v>30</v>
-      </c>
-      <c r="F2" t="str">
-        <v>32</v>
-      </c>
-      <c r="G2" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Ice</v>
-      </c>
-      <c r="B3" t="str">
-        <v>28</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D3" t="str">
-        <v>26</v>
-      </c>
-      <c r="E3" t="str">
-        <v>30</v>
-      </c>
-      <c r="F3" t="str">
-        <v>32</v>
-      </c>
-      <c r="G3" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Black-baggy</v>
-      </c>
-      <c r="B4" t="str">
-        <v>28</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D4" t="str">
-        <v>26</v>
-      </c>
-      <c r="E4" t="str">
-        <v>30</v>
-      </c>
-      <c r="F4" t="str">
-        <v>32</v>
-      </c>
-      <c r="G4" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Black-Plain</v>
-      </c>
-      <c r="B5" t="str">
-        <v>28</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D5" t="str">
-        <v>26</v>
-      </c>
-      <c r="E5" t="str">
-        <v>30</v>
-      </c>
-      <c r="F5" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>White-Plain</v>
-      </c>
-      <c r="B6" t="str">
-        <v>28</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D6" t="str">
-        <v>26</v>
-      </c>
-      <c r="E6" t="str">
-        <v>30</v>
-      </c>
-      <c r="F6" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Trouser</v>
-      </c>
-      <c r="B7" t="str">
-        <v>28</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D7" t="str">
-        <v>30</v>
-      </c>
-      <c r="E7" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Trouser</v>
-      </c>
-      <c r="B8" t="str">
-        <v>M</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Regular</v>
-      </c>
-      <c r="D8" t="str">
-        <v>L</v>
-      </c>
-      <c r="E8" t="str">
-        <v>XL</v>
+    <row r="1" spans="1:7" ht="15.75">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError sqref="A1:G6 A8:G8 A7:B7 D7:G7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -604,94 +654,71 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="1" max="26" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>column</v>
-      </c>
-      <c r="B1" t="str">
-        <v>purpose</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>kind</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Row selector field</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>size</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Row selector field</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>variant_qualifier</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Fills the Select Unit combobox</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>size_variant_1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>First size variant to create</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>size_variant_2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Second size variant to create</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>size_variant_3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Third size variant to create</v>
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError sqref="A1:B7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,116 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="525" windowWidth="19815" windowHeight="7365"/>
-  </bookViews>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>variant_qualifier</t>
-  </si>
-  <si>
-    <t>size_variant_1</t>
-  </si>
-  <si>
-    <t>size_variant_2</t>
-  </si>
-  <si>
-    <t>size_variant_3</t>
-  </si>
-  <si>
-    <t>size_variant_4</t>
-  </si>
-  <si>
-    <t>Beige</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>Black-baggy</t>
-  </si>
-  <si>
-    <t>Black-Plain</t>
-  </si>
-  <si>
-    <t>White-Plain</t>
-  </si>
-  <si>
-    <t>Trouser</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>purpose</t>
-  </si>
-  <si>
-    <t>Row selector field</t>
-  </si>
-  <si>
-    <t>Fills the Select Unit combobox</t>
-  </si>
-  <si>
-    <t>First size variant to create</t>
-  </si>
-  <si>
-    <t>Second size variant to create</t>
-  </si>
-  <si>
-    <t>Third size variant to create</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -474,179 +399,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
-    <col min="2" max="26" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="B1" t="str">
+        <v>size</v>
+      </c>
+      <c r="C1" t="str">
+        <v>variant_qualifier</v>
+      </c>
+      <c r="D1" t="str">
+        <v>size_variant_1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>size_variant_2</v>
+      </c>
+      <c r="F1" t="str">
+        <v>size_variant_3</v>
+      </c>
+      <c r="G1" t="str">
+        <v>size_variant_4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Beige</v>
+      </c>
+      <c r="B2" t="str">
+        <v>28</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D2" t="str">
+        <v>26</v>
+      </c>
+      <c r="E2" t="str">
+        <v>30</v>
+      </c>
+      <c r="F2" t="str">
+        <v>32</v>
+      </c>
+      <c r="G2" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="B3" t="str">
+        <v>28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D3" t="str">
+        <v>26</v>
+      </c>
+      <c r="E3" t="str">
+        <v>30</v>
+      </c>
+      <c r="F3" t="str">
+        <v>32</v>
+      </c>
+      <c r="G3" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Black-baggy</v>
+      </c>
+      <c r="B4" t="str">
+        <v>28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D4" t="str">
+        <v>26</v>
+      </c>
+      <c r="E4" t="str">
+        <v>30</v>
+      </c>
+      <c r="F4" t="str">
+        <v>32</v>
+      </c>
+      <c r="G4" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Black-Plain</v>
+      </c>
+      <c r="B5" t="str">
+        <v>28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D5" t="str">
+        <v>26</v>
+      </c>
+      <c r="E5" t="str">
+        <v>30</v>
+      </c>
+      <c r="F5" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>White-Plain</v>
+      </c>
+      <c r="B6" t="str">
+        <v>28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D6" t="str">
+        <v>26</v>
+      </c>
+      <c r="E6" t="str">
+        <v>30</v>
+      </c>
+      <c r="F6" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Trouser</v>
+      </c>
+      <c r="B7" t="str">
+        <v>28</v>
+      </c>
+      <c r="D7" t="str">
+        <v>30</v>
+      </c>
+      <c r="E7" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Trouser</v>
+      </c>
+      <c r="B8" t="str">
+        <v>M</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="D8" t="str">
+        <v>L</v>
+      </c>
+      <c r="E8" t="str">
+        <v>XL</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G6 A8:G8 A7:B7 D7:G7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -654,71 +601,94 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>purpose</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>kind</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Row selector field</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>size</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Row selector field</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>variant_qualifier</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Fills the Select Unit combobox</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>size_variant_1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>First size variant to create</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>size_variant_2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Second size variant to create</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>size_variant_3</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Third size variant to create</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -400,13 +400,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.83203125" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+    <col min="7" max="7" width="34.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
@@ -590,6 +590,9 @@
       <c r="E8" t="str">
         <v>XL</v>
       </c>
+      <c r="F8" t="str">
+        <v>S</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -602,8 +605,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>

--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,41 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="525" windowWidth="19815" windowHeight="7365"/>
+  </bookViews>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>variant_qualifier</t>
+  </si>
+  <si>
+    <t>size_variant_1</t>
+  </si>
+  <si>
+    <t>size_variant_2</t>
+  </si>
+  <si>
+    <t>size_variant_3</t>
+  </si>
+  <si>
+    <t>size_variant_4</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>Black-baggy</t>
+  </si>
+  <si>
+    <t>Black-Plain</t>
+  </si>
+  <si>
+    <t>White-Plain</t>
+  </si>
+  <si>
+    <t>Trouser</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>purpose</t>
+  </si>
+  <si>
+    <t>Row selector field</t>
+  </si>
+  <si>
+    <t>Fills the Select Unit combobox</t>
+  </si>
+  <si>
+    <t>First size variant to create</t>
+  </si>
+  <si>
+    <t>Second size variant to create</t>
+  </si>
+  <si>
+    <t>Third size variant to create</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -399,204 +477,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
-    <col min="5" max="5" width="34.83203125" customWidth="1"/>
-    <col min="6" max="6" width="34.83203125" customWidth="1"/>
-    <col min="7" max="7" width="34.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.125" customWidth="1"/>
+    <col min="2" max="7" width="34.875" customWidth="1"/>
+    <col min="8" max="26" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>kind</v>
-      </c>
-      <c r="B1" t="str">
-        <v>size</v>
-      </c>
-      <c r="C1" t="str">
-        <v>variant_qualifier</v>
-      </c>
-      <c r="D1" t="str">
-        <v>size_variant_1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>size_variant_2</v>
-      </c>
-      <c r="F1" t="str">
-        <v>size_variant_3</v>
-      </c>
-      <c r="G1" t="str">
-        <v>size_variant_4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Beige</v>
-      </c>
-      <c r="B2" t="str">
-        <v>28</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D2" t="str">
+    <row r="1" spans="1:7" ht="15.75">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
         <v>26</v>
       </c>
-      <c r="E2" t="str">
-        <v>30</v>
-      </c>
-      <c r="F2" t="str">
-        <v>32</v>
-      </c>
-      <c r="G2" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Ice</v>
-      </c>
-      <c r="B3" t="str">
-        <v>28</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D3" t="str">
-        <v>26</v>
-      </c>
-      <c r="E3" t="str">
-        <v>30</v>
-      </c>
-      <c r="F3" t="str">
-        <v>32</v>
-      </c>
-      <c r="G3" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Black-baggy</v>
-      </c>
-      <c r="B4" t="str">
-        <v>28</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D4" t="str">
-        <v>26</v>
-      </c>
-      <c r="E4" t="str">
-        <v>30</v>
-      </c>
-      <c r="F4" t="str">
-        <v>32</v>
-      </c>
-      <c r="G4" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Black-Plain</v>
-      </c>
-      <c r="B5" t="str">
-        <v>28</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D5" t="str">
-        <v>26</v>
-      </c>
-      <c r="E5" t="str">
-        <v>30</v>
-      </c>
-      <c r="F5" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>White-Plain</v>
-      </c>
-      <c r="B6" t="str">
-        <v>28</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D6" t="str">
-        <v>26</v>
-      </c>
-      <c r="E6" t="str">
-        <v>30</v>
-      </c>
-      <c r="F6" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Trouser</v>
-      </c>
-      <c r="B7" t="str">
-        <v>28</v>
-      </c>
-      <c r="D7" t="str">
-        <v>30</v>
-      </c>
-      <c r="E7" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Trouser</v>
-      </c>
-      <c r="B8" t="str">
-        <v>M</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Regular</v>
-      </c>
-      <c r="D8" t="str">
-        <v>L</v>
-      </c>
-      <c r="E8" t="str">
-        <v>XL</v>
-      </c>
-      <c r="F8" t="str">
-        <v>S</v>
+    </row>
+    <row r="8" spans="1:7" ht="15.75">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError sqref="A1:G6 A8:G8 A7:E7 G7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -604,94 +664,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="1" max="2" width="34.875" customWidth="1"/>
+    <col min="3" max="26" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>column</v>
-      </c>
-      <c r="B1" t="str">
-        <v>purpose</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>kind</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Row selector field</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>size</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Row selector field</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>variant_qualifier</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Fills the Select Unit combobox</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>size_variant_1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>First size variant to create</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>size_variant_2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Second size variant to create</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>size_variant_3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Third size variant to create</v>
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError sqref="A1:B7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,119 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="525" windowWidth="19815" windowHeight="7365"/>
-  </bookViews>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>variant_qualifier</t>
-  </si>
-  <si>
-    <t>size_variant_1</t>
-  </si>
-  <si>
-    <t>size_variant_2</t>
-  </si>
-  <si>
-    <t>size_variant_3</t>
-  </si>
-  <si>
-    <t>size_variant_4</t>
-  </si>
-  <si>
-    <t>Beige</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Ice</t>
-  </si>
-  <si>
-    <t>Black-baggy</t>
-  </si>
-  <si>
-    <t>Black-Plain</t>
-  </si>
-  <si>
-    <t>White-Plain</t>
-  </si>
-  <si>
-    <t>Trouser</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>purpose</t>
-  </si>
-  <si>
-    <t>Row selector field</t>
-  </si>
-  <si>
-    <t>Fills the Select Unit combobox</t>
-  </si>
-  <si>
-    <t>First size variant to create</t>
-  </si>
-  <si>
-    <t>Second size variant to create</t>
-  </si>
-  <si>
-    <t>Third size variant to create</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -477,186 +399,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.125" customWidth="1"/>
-    <col min="2" max="7" width="34.875" customWidth="1"/>
-    <col min="8" max="26" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="41.50390625" customWidth="1"/>
+    <col min="3" max="3" width="41.50390625" customWidth="1"/>
+    <col min="4" max="4" width="41.50390625" customWidth="1"/>
+    <col min="5" max="5" width="41.50390625" customWidth="1"/>
+    <col min="6" max="6" width="41.50390625" customWidth="1"/>
+    <col min="7" max="7" width="41.50390625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="B1" t="str">
+        <v>size</v>
+      </c>
+      <c r="C1" t="str">
+        <v>variant_qualifier</v>
+      </c>
+      <c r="D1" t="str">
+        <v>size_variant_1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>size_variant_2</v>
+      </c>
+      <c r="F1" t="str">
+        <v>size_variant_3</v>
+      </c>
+      <c r="G1" t="str">
+        <v>size_variant_4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Beige</v>
+      </c>
+      <c r="B2" t="str">
+        <v>28</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D2" t="str">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
+      <c r="E2" t="str">
+        <v>30</v>
+      </c>
+      <c r="F2" t="str">
+        <v>32</v>
+      </c>
+      <c r="G2" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="B3" t="str">
+        <v>28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D3" t="str">
+        <v>26</v>
+      </c>
+      <c r="E3" t="str">
+        <v>30</v>
+      </c>
+      <c r="F3" t="str">
+        <v>32</v>
+      </c>
+      <c r="G3" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Black-baggy</v>
+      </c>
+      <c r="B4" t="str">
+        <v>28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D4" t="str">
+        <v>26</v>
+      </c>
+      <c r="E4" t="str">
+        <v>30</v>
+      </c>
+      <c r="F4" t="str">
+        <v>32</v>
+      </c>
+      <c r="G4" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Black-Plain</v>
+      </c>
+      <c r="B5" t="str">
+        <v>28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D5" t="str">
+        <v>26</v>
+      </c>
+      <c r="E5" t="str">
+        <v>30</v>
+      </c>
+      <c r="F5" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>White-Plain</v>
+      </c>
+      <c r="B6" t="str">
+        <v>28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Number</v>
+      </c>
+      <c r="D6" t="str">
+        <v>26</v>
+      </c>
+      <c r="E6" t="str">
+        <v>30</v>
+      </c>
+      <c r="F6" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Trouser</v>
+      </c>
+      <c r="B7" t="str">
+        <v>28</v>
+      </c>
+      <c r="D7" t="str">
+        <v>30</v>
+      </c>
+      <c r="E7" t="str">
+        <v>32</v>
+      </c>
+      <c r="F7" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Trouser</v>
+      </c>
+      <c r="B8" t="str">
+        <v>M</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="D8" t="str">
+        <v>L</v>
+      </c>
+      <c r="E8" t="str">
+        <v>XL</v>
+      </c>
+      <c r="F8" t="str">
+        <v>S</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G6 A8:G8 A7:E7 G7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,72 +607,94 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="34.875" customWidth="1"/>
-    <col min="3" max="26" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="41.50390625" customWidth="1"/>
+    <col min="2" max="2" width="41.50390625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>purpose</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>kind</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Row selector field</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>size</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Row selector field</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>variant_qualifier</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Fills the Select Unit combobox</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>size_variant_1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>First size variant to create</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>size_variant_2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Second size variant to create</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>size_variant_3</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Third size variant to create</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,42 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0F5B3513E9574E14FEC18C6D6074A9F54027CA0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>variant_qualifier</t>
+  </si>
+  <si>
+    <t>size_variant_1</t>
+  </si>
+  <si>
+    <t>size_variant_2</t>
+  </si>
+  <si>
+    <t>size_variant_3</t>
+  </si>
+  <si>
+    <t>size_variant_4</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>Black-baggy</t>
+  </si>
+  <si>
+    <t>Black-Plain</t>
+  </si>
+  <si>
+    <t>White-Plain</t>
+  </si>
+  <si>
+    <t>Trouser</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>purpose</t>
+  </si>
+  <si>
+    <t>Row selector field</t>
+  </si>
+  <si>
+    <t>Fills the Select Unit combobox</t>
+  </si>
+  <si>
+    <t>First size variant to create</t>
+  </si>
+  <si>
+    <t>Second size variant to create</t>
+  </si>
+  <si>
+    <t>Third size variant to create</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,13 +150,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,304 +489,261 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" customWidth="1"/>
-    <col min="2" max="2" width="41.50390625" customWidth="1"/>
-    <col min="3" max="3" width="41.50390625" customWidth="1"/>
-    <col min="4" max="4" width="41.50390625" customWidth="1"/>
-    <col min="5" max="5" width="41.50390625" customWidth="1"/>
-    <col min="6" max="6" width="41.50390625" customWidth="1"/>
-    <col min="7" max="7" width="41.50390625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="34.796875" customWidth="1"/>
+    <col min="2" max="7" width="41.5" customWidth="1"/>
+    <col min="8" max="26" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>kind</v>
-      </c>
-      <c r="B1" t="str">
-        <v>size</v>
-      </c>
-      <c r="C1" t="str">
-        <v>variant_qualifier</v>
-      </c>
-      <c r="D1" t="str">
-        <v>size_variant_1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>size_variant_2</v>
-      </c>
-      <c r="F1" t="str">
-        <v>size_variant_3</v>
-      </c>
-      <c r="G1" t="str">
-        <v>size_variant_4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Beige</v>
-      </c>
-      <c r="B2" t="str">
-        <v>28</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D2" t="str">
-        <v>26</v>
-      </c>
-      <c r="E2" t="str">
-        <v>30</v>
-      </c>
-      <c r="F2" t="str">
-        <v>32</v>
-      </c>
-      <c r="G2" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Ice</v>
-      </c>
-      <c r="B3" t="str">
-        <v>28</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D3" t="str">
-        <v>26</v>
-      </c>
-      <c r="E3" t="str">
-        <v>30</v>
-      </c>
-      <c r="F3" t="str">
-        <v>32</v>
-      </c>
-      <c r="G3" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Black-baggy</v>
-      </c>
-      <c r="B4" t="str">
-        <v>28</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D4" t="str">
-        <v>26</v>
-      </c>
-      <c r="E4" t="str">
-        <v>30</v>
-      </c>
-      <c r="F4" t="str">
-        <v>32</v>
-      </c>
-      <c r="G4" t="str">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Black-Plain</v>
-      </c>
-      <c r="B5" t="str">
-        <v>28</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D5" t="str">
-        <v>26</v>
-      </c>
-      <c r="E5" t="str">
-        <v>30</v>
-      </c>
-      <c r="F5" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>White-Plain</v>
-      </c>
-      <c r="B6" t="str">
-        <v>28</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Number</v>
-      </c>
-      <c r="D6" t="str">
-        <v>26</v>
-      </c>
-      <c r="E6" t="str">
-        <v>30</v>
-      </c>
-      <c r="F6" t="str">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Trouser</v>
-      </c>
-      <c r="B7" t="str">
-        <v>28</v>
-      </c>
-      <c r="D7" t="str">
-        <v>30</v>
-      </c>
-      <c r="E7" t="str">
-        <v>32</v>
-      </c>
-      <c r="F7" t="str">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Trouser</v>
-      </c>
-      <c r="B8" t="str">
-        <v>M</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Regular</v>
-      </c>
-      <c r="D8" t="str">
-        <v>L</v>
-      </c>
-      <c r="E8" t="str">
-        <v>XL</v>
-      </c>
-      <c r="F8" t="str">
-        <v>S</v>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError sqref="A1:G8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.50390625" customWidth="1"/>
-    <col min="2" max="2" width="41.50390625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" customWidth="1"/>
+    <col min="1" max="2" width="41.5" customWidth="1"/>
+    <col min="3" max="26" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>column</v>
-      </c>
-      <c r="B1" t="str">
-        <v>purpose</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>kind</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Row selector field</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>size</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Row selector field</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>variant_qualifier</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Fills the Select Unit combobox</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>size_variant_1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>First size variant to create</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>size_variant_2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Second size variant to create</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>size_variant_3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Third size variant to create</v>
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError sqref="A1:B7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,27 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0F5B3513E9574E14FEC18C6D6074A9F54027CA0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
-    <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Jeans Variant Inputs" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Jeans Variant Guide" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>kind</t>
   </si>
@@ -47,24 +38,9 @@
     <t>Beige</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>Number</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>Ice</t>
   </si>
   <si>
@@ -93,6 +69,9 @@
   </si>
   <si>
     <t>S</t>
+  </si>
+  <si>
+    <t>Track Pant</t>
   </si>
   <si>
     <t>column</t>
@@ -119,14 +98,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,7 +135,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -489,16 +468,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34.796875" customWidth="1"/>
-    <col min="2" max="7" width="41.5" customWidth="1"/>
-    <col min="8" max="26" width="16.69921875" customWidth="1"/>
+    <col min="1" max="1" width="34.857142857142854" customWidth="1"/>
+    <col min="2" max="7" width="41.57142857142857" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,229 +500,245 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>26</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>32</v>
+      </c>
+      <c r="G2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>32</v>
+      </c>
+      <c r="G3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <v>32</v>
+      </c>
+      <c r="G4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B6">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G8" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="41.5" customWidth="1"/>
-    <col min="3" max="26" width="16.69921875" customWidth="1"/>
+    <col min="1" max="2" width="41.57142857142857" customWidth="1"/>
+    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:B7" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
+++ b/Full-LC-AUTO/data inputs/common/Variants-excel.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107FE6EB-9EFF-4127-BBB0-B480A0E186EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Jeans Variant Inputs" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Jeans Variant Guide" state="visible" r:id="rId5"/>
+    <sheet name="Jeans Variant Inputs" sheetId="1" r:id="rId1"/>
+    <sheet name="Jeans Variant Guide" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>kind</t>
   </si>
@@ -93,19 +97,22 @@
   </si>
   <si>
     <t>Third size variant to create</t>
+  </si>
+  <si>
+    <t>White-baggy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -468,16 +475,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.857142857142854" customWidth="1"/>
-    <col min="2" max="7" width="41.57142857142857" customWidth="1"/>
-    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="34.88671875" customWidth="1"/>
+    <col min="2" max="7" width="41.5546875" customWidth="1"/>
+    <col min="8" max="24" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -523,7 +530,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -546,7 +553,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -569,7 +576,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -589,7 +596,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -609,46 +616,52 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>28</v>
       </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
       <c r="D7">
+        <v>26</v>
+      </c>
+      <c r="E7">
         <v>30</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>32</v>
       </c>
-      <c r="F7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
+      <c r="B8">
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -666,22 +679,42 @@
         <v>18</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="41.57142857142857" customWidth="1"/>
-    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="2" width="41.5546875" customWidth="1"/>
+    <col min="3" max="24" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -689,7 +722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -697,7 +730,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -705,7 +738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -713,7 +746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -721,7 +754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -729,7 +762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -739,6 +772,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>